--- a/docs/フリマ出品支援アプリ企画および仕様設計.xlsx
+++ b/docs/フリマ出品支援アプリ企画および仕様設計.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12330" tabRatio="851" firstSheet="1" activeTab="11"/>
+    <workbookView windowWidth="28125" windowHeight="12330" tabRatio="865" firstSheet="1" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="アプリ案ドラフト" sheetId="1" r:id="rId1"/>
@@ -19,13 +19,14 @@
     <sheet name="ファイル構成" sheetId="11" r:id="rId10"/>
     <sheet name="DB設計(ER図)" sheetId="12" r:id="rId11"/>
     <sheet name="DB設計(テーブル定義書)" sheetId="13" r:id="rId12"/>
+    <sheet name="追加機能" sheetId="14" r:id="rId13"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="816">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1255" uniqueCount="831">
   <si>
     <t>（出品自体は説明文をコピペして手作業で出品）</t>
   </si>
@@ -3113,16 +3114,61 @@
   <si>
     <t>image_url</t>
   </si>
+  <si>
+    <t>【追加機能案】</t>
+  </si>
+  <si>
+    <t>・ボタンにホバーした時にcursor: pointer; をつける＆CSSアニメーションがあるなどボタンが押せそうなUIにしたい</t>
+  </si>
+  <si>
+    <t>https://coosy.co.jp/blog/css-hovereffect/</t>
+  </si>
+  <si>
+    <t>https://rilaks.jp/blog/mouse-over/</t>
+  </si>
+  <si>
+    <t>・生成が終了したらフォームの中身をクリアしたい</t>
+  </si>
+  <si>
+    <t>【Agent向け指示】</t>
+  </si>
+  <si>
+    <t>（feature/mouseoverブランチを作成）</t>
+  </si>
+  <si>
+    <t>・すべてのボタンについて、マウスオーバー時にCursor: pointerとしてください。</t>
+  </si>
+  <si>
+    <t>・履歴の削除以外のボタンについて、マウスオーバー時の背景色変化が小さくて見づらいので、もう少し変化がはっきり見えるように変更してください。</t>
+  </si>
+  <si>
+    <t>・上記以外は極力コード変更しないでください。</t>
+  </si>
+  <si>
+    <t>・その他ロジック変更禁止、API変更禁止、DB変更禁止、大規模リファクタは必要な範囲のみ</t>
+  </si>
+  <si>
+    <t>・Agent.mdにしたがってください</t>
+  </si>
+  <si>
+    <t>（feature/formclearブランチを作成）</t>
+  </si>
+  <si>
+    <t>・生成するを押して生成が完了したら「入力」カードの画像と商品メモ・キーワードをクリアしてください。</t>
+  </si>
+  <si>
+    <t>・その代わり「今回の生成結果」カードに、「生成用入力」という欄を作って、画像と商品メモ・キーワードを表示してください。</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -3130,6 +3176,14 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3194,20 +3248,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -3224,21 +3264,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -3247,14 +3278,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3308,8 +3346,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3325,6 +3364,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -3351,30 +3397,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -3387,7 +3409,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3399,13 +3493,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3417,73 +3523,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3495,13 +3535,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3513,13 +3559,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3531,7 +3571,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3592,11 +3638,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3619,15 +3663,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
@@ -3639,6 +3674,17 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -3665,207 +3711,201 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="8" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4801,147 +4841,147 @@
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>756</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>757</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>758</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>759</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>760</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>761</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>762</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>763</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>764</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>765</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>766</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="4" t="s">
         <v>767</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="4" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="4" t="s">
         <v>769</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="4" t="s">
         <v>770</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>771</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="4" t="s">
         <v>772</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="4" t="s">
         <v>773</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="4" t="s">
         <v>774</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>775</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>776</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="4" t="s">
         <v>777</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="4" t="s">
         <v>759</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="4" t="s">
         <v>778</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="4" t="s">
         <v>779</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="4" t="s">
         <v>768</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="4" t="s">
         <v>780</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="4" t="s">
         <v>781</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="4" t="s">
         <v>775</v>
       </c>
     </row>
@@ -5040,444 +5080,444 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>784</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>786</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>792</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>645</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>793</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>794</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>795</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>796</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
         <v>794</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="3" t="s">
         <v>661</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>664</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>798</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="3" t="s">
         <v>669</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>799</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="3" t="s">
         <v>800</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="3" t="s">
         <v>684</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>686</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="3" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>688</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="F14" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="3" t="s">
         <v>689</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="F15" s="3" t="s">
         <v>801</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="3" t="s">
         <v>802</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="3" t="s">
         <v>794</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="3" t="s">
         <v>803</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="3" t="s">
         <v>706</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>718</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>720</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F17" s="2" t="b">
+      <c r="F17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="3" t="s">
         <v>719</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="3" t="s">
         <v>804</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="3" t="s">
         <v>806</v>
       </c>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="3" t="s">
         <v>696</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="3" t="s">
         <v>807</v>
       </c>
     </row>
@@ -5492,204 +5532,310 @@
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>784</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="2" t="s">
         <v>786</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="2" t="s">
         <v>787</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="2" t="s">
         <v>789</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="2" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="H25" s="3" t="s">
         <v>645</v>
       </c>
     </row>
     <row r="26" ht="27" spans="1:8">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="3" t="s">
         <v>810</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="3" t="s">
         <v>792</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="H26" s="3" t="s">
         <v>811</v>
       </c>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>812</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H27" s="2"/>
+      <c r="H27" s="3"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>686</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H28" s="2"/>
+      <c r="H28" s="3"/>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>813</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" s="3" t="s">
         <v>794</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="3" t="s">
         <v>814</v>
       </c>
-      <c r="H29" s="2"/>
+      <c r="H29" s="3"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
         <v>815</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" s="3" t="s">
         <v>794</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="H30" s="2"/>
+      <c r="H30" s="3"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="H31" s="2"/>
+      <c r="H31" s="3"/>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2">
+      <c r="B3" s="1" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2">
+      <c r="B4" s="1" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>827</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" display="https://coosy.co.jp/blog/css-hovereffect/"/>
+    <hyperlink ref="B4" r:id="rId2" display="https://rilaks.jp/blog/mouse-over/"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -5707,22 +5853,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="28.5" spans="1:1">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" ht="21" spans="1:1">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="7" ht="21" spans="1:1">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="9" ht="17.25" spans="1:1">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="9" t="s">
         <v>4</v>
       </c>
     </row>
@@ -5732,7 +5878,7 @@
       </c>
     </row>
     <row r="13" ht="17.25" spans="1:1">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="9" t="s">
         <v>5</v>
       </c>
     </row>
@@ -5742,107 +5888,107 @@
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="12" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="18" ht="17.25" spans="1:1">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="8" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="26" ht="17.25" spans="1:1">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="8" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="34" ht="21" spans="1:1">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="36" ht="17.25" spans="1:1">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="9" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="8" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="8" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="46" ht="17.25" spans="1:1">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="9" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="10" t="s">
+      <c r="A48" s="8" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="10" t="s">
+      <c r="A50" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="54" ht="21" spans="1:1">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="58" ht="21" spans="1:1">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="60" ht="17.25" spans="1:1">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="9" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="62" ht="14.25" spans="1:1">
-      <c r="A62" s="17" t="s">
+      <c r="A62" s="15" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5852,37 +5998,37 @@
       </c>
     </row>
     <row r="66" ht="14.25" spans="1:1">
-      <c r="A66" s="17" t="s">
+      <c r="A66" s="15" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="10" t="s">
+      <c r="A68" s="8" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="10" t="s">
+      <c r="A70" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="10" t="s">
+      <c r="A72" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="10" t="s">
+      <c r="A74" s="8" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="78" ht="17.25" spans="1:1">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="9" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="80" ht="14.25" spans="1:1">
-      <c r="A80" s="17" t="s">
+      <c r="A80" s="15" t="s">
         <v>27</v>
       </c>
     </row>
@@ -5892,136 +6038,136 @@
       </c>
     </row>
     <row r="84" ht="14.25" spans="1:1">
-      <c r="A84" s="17" t="s">
+      <c r="A84" s="15" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="10" t="s">
+      <c r="A86" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="88" spans="1:1">
-      <c r="A88" s="10" t="s">
+      <c r="A88" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="18" t="s">
+      <c r="A90" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="18" t="s">
+      <c r="A92" s="16" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="18" t="s">
+      <c r="A94" s="16" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="18" t="s">
+      <c r="A96" s="16" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="98" ht="14.25" spans="1:1">
-      <c r="A98" s="17" t="s">
+      <c r="A98" s="15" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="100" spans="1:2">
-      <c r="A100" s="19" t="s">
+      <c r="A100" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B100" s="19" t="s">
+      <c r="B100" s="17" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="5" t="s">
+      <c r="A101" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B101" s="5" t="s">
+      <c r="B101" s="3" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="102" spans="1:2">
-      <c r="A102" s="5" t="s">
+      <c r="A102" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="B102" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="5" t="s">
+      <c r="A103" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B103" s="5" t="s">
+      <c r="B103" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="104" spans="1:2">
-      <c r="A104" s="5" t="s">
+      <c r="A104" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="B104" s="3" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="5" t="s">
+      <c r="A105" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B105" s="5" t="s">
+      <c r="B105" s="3" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="106" spans="1:2">
-      <c r="A106" s="5" t="s">
+      <c r="A106" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B106" s="5" t="s">
+      <c r="B106" s="3" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="5" t="s">
+      <c r="A107" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B107" s="5" t="s">
+      <c r="B107" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="109" ht="14.25" spans="1:1">
-      <c r="A109" s="17" t="s">
+      <c r="A109" s="15" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="10" t="s">
+      <c r="A111" s="8" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="10" t="s">
+      <c r="A113" s="8" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="10" t="s">
+      <c r="A115" s="8" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="119" ht="17.25" spans="1:1">
-      <c r="A119" s="11" t="s">
+      <c r="A119" s="9" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="121" ht="14.25" spans="1:1">
-      <c r="A121" s="17" t="s">
+      <c r="A121" s="15" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6031,37 +6177,37 @@
       </c>
     </row>
     <row r="125" ht="14.25" spans="1:1">
-      <c r="A125" s="17" t="s">
+      <c r="A125" s="15" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="127" spans="1:1">
-      <c r="A127" s="10" t="s">
+      <c r="A127" s="8" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" s="10" t="s">
+      <c r="A129" s="8" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" s="10" t="s">
+      <c r="A131" s="8" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="135" ht="21" spans="1:1">
-      <c r="A135" s="8" t="s">
+      <c r="A135" s="7" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="139" ht="17.25" spans="1:1">
-      <c r="A139" s="11" t="s">
+      <c r="A139" s="9" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="141" ht="14.25" spans="1:1">
-      <c r="A141" s="17" t="s">
+      <c r="A141" s="15" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6071,67 +6217,67 @@
       </c>
     </row>
     <row r="145" ht="14.25" spans="1:1">
-      <c r="A145" s="17" t="s">
+      <c r="A145" s="15" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="147" spans="1:1">
-      <c r="A147" s="10" t="s">
+      <c r="A147" s="8" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="10" t="s">
+      <c r="A149" s="8" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="151" ht="14.25" spans="1:1">
-      <c r="A151" s="17" t="s">
+      <c r="A151" s="15" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="153" spans="1:1">
-      <c r="A153" s="10" t="s">
+      <c r="A153" s="8" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="155" spans="1:1">
-      <c r="A155" s="18" t="s">
+      <c r="A155" s="16" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="157" spans="1:1">
-      <c r="A157" s="18" t="s">
+      <c r="A157" s="16" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="159" spans="1:1">
-      <c r="A159" s="18" t="s">
+      <c r="A159" s="16" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="161" ht="14.25" spans="1:1">
-      <c r="A161" s="17" t="s">
+      <c r="A161" s="15" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="163" spans="1:1">
-      <c r="A163" s="10" t="s">
+      <c r="A163" s="8" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="165" spans="1:1">
-      <c r="A165" s="10" t="s">
+      <c r="A165" s="8" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="169" ht="17.25" spans="1:1">
-      <c r="A169" s="11" t="s">
+      <c r="A169" s="9" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="171" ht="14.25" spans="1:1">
-      <c r="A171" s="17" t="s">
+      <c r="A171" s="15" t="s">
         <v>27</v>
       </c>
     </row>
@@ -6141,47 +6287,47 @@
       </c>
     </row>
     <row r="175" ht="14.25" spans="1:1">
-      <c r="A175" s="17" t="s">
+      <c r="A175" s="15" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="177" spans="1:1">
-      <c r="A177" s="10" t="s">
+      <c r="A177" s="8" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="179" spans="1:1">
-      <c r="A179" s="10" t="s">
+      <c r="A179" s="8" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="181" spans="1:1">
-      <c r="A181" s="10" t="s">
+      <c r="A181" s="8" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="183" spans="1:1">
-      <c r="A183" s="10" t="s">
+      <c r="A183" s="8" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="185" ht="14.25" spans="1:1">
-      <c r="A185" s="17" t="s">
+      <c r="A185" s="15" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="187" spans="1:1">
-      <c r="A187" s="10" t="s">
+      <c r="A187" s="8" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="191" ht="17.25" spans="1:1">
-      <c r="A191" s="11" t="s">
+      <c r="A191" s="9" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="193" ht="14.25" spans="1:1">
-      <c r="A193" s="17" t="s">
+      <c r="A193" s="15" t="s">
         <v>90</v>
       </c>
     </row>
@@ -6191,438 +6337,438 @@
       </c>
     </row>
     <row r="197" ht="14.25" spans="1:1">
-      <c r="A197" s="17" t="s">
+      <c r="A197" s="15" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="199" spans="1:1">
-      <c r="A199" s="10" t="s">
+      <c r="A199" s="8" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="201" spans="1:1">
-      <c r="A201" s="10" t="s">
+      <c r="A201" s="8" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="203" ht="14.25" spans="1:1">
-      <c r="A203" s="17" t="s">
+      <c r="A203" s="15" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="205" spans="1:1">
-      <c r="A205" s="10" t="s">
+      <c r="A205" s="8" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="207" spans="1:1">
-      <c r="A207" s="10" t="s">
+      <c r="A207" s="8" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="211" ht="21" spans="1:1">
-      <c r="A211" s="8" t="s">
+      <c r="A211" s="7" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="215" ht="17.25" spans="1:1">
-      <c r="A215" s="11" t="s">
+      <c r="A215" s="9" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="217" spans="1:1">
-      <c r="A217" s="10" t="s">
+      <c r="A217" s="8" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="219" ht="17.25" spans="1:1">
-      <c r="A219" s="11" t="s">
+      <c r="A219" s="9" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="221" spans="1:1">
-      <c r="A221" s="10" t="s">
+      <c r="A221" s="8" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="223" ht="17.25" spans="1:1">
-      <c r="A223" s="11" t="s">
+      <c r="A223" s="9" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="225" spans="1:1">
-      <c r="A225" s="10" t="s">
+      <c r="A225" s="8" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="227" spans="1:1">
-      <c r="A227" s="10" t="s">
+      <c r="A227" s="8" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="229" ht="17.25" spans="1:1">
-      <c r="A229" s="11" t="s">
+      <c r="A229" s="9" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="231" spans="1:1">
-      <c r="A231" s="10" t="s">
+      <c r="A231" s="8" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="233" spans="1:1">
-      <c r="A233" s="10" t="s">
+      <c r="A233" s="8" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="237" ht="21" spans="1:1">
-      <c r="A237" s="8" t="s">
+      <c r="A237" s="7" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="239" ht="17.25" spans="1:1">
-      <c r="A239" s="11" t="s">
+      <c r="A239" s="9" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="241" spans="1:3">
-      <c r="A241" s="19" t="s">
+      <c r="A241" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="B241" s="19" t="s">
+      <c r="B241" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="C241" s="19" t="s">
+      <c r="C241" s="17" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="242" spans="1:3">
-      <c r="A242" s="5" t="s">
+      <c r="A242" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B242" s="5" t="s">
+      <c r="B242" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C242" s="5" t="s">
+      <c r="C242" s="3" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="243" spans="1:3">
-      <c r="A243" s="5" t="s">
+      <c r="A243" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B243" s="5" t="s">
+      <c r="B243" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C243" s="5" t="s">
+      <c r="C243" s="3" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="244" spans="1:3">
-      <c r="A244" s="5" t="s">
+      <c r="A244" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B244" s="5" t="s">
+      <c r="B244" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C244" s="5" t="s">
+      <c r="C244" s="3" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="245" spans="1:3">
-      <c r="A245" s="5" t="s">
+      <c r="A245" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B245" s="5" t="s">
+      <c r="B245" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C245" s="5" t="s">
+      <c r="C245" s="3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="246" spans="1:3">
-      <c r="A246" s="5" t="s">
+      <c r="A246" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B246" s="5" t="s">
+      <c r="B246" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C246" s="5" t="s">
+      <c r="C246" s="3" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="247" spans="1:3">
-      <c r="A247" s="5" t="s">
+      <c r="A247" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B247" s="5" t="s">
+      <c r="B247" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C247" s="5" t="s">
+      <c r="C247" s="3" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="248" spans="1:3">
-      <c r="A248" s="5" t="s">
+      <c r="A248" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B248" s="5" t="s">
+      <c r="B248" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C248" s="5" t="s">
+      <c r="C248" s="3" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="249" spans="1:3">
-      <c r="A249" s="5" t="s">
+      <c r="A249" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B249" s="5" t="s">
+      <c r="B249" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C249" s="5" t="s">
+      <c r="C249" s="3" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="250" spans="1:3">
-      <c r="A250" s="5" t="s">
+      <c r="A250" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B250" s="5" t="s">
+      <c r="B250" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C250" s="5" t="s">
+      <c r="C250" s="3" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="251" spans="1:3">
-      <c r="A251" s="5" t="s">
+      <c r="A251" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B251" s="5" t="s">
+      <c r="B251" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C251" s="5" t="s">
+      <c r="C251" s="3" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="254" ht="21" spans="1:1">
-      <c r="A254" s="8" t="s">
+      <c r="A254" s="7" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="256" spans="1:2">
-      <c r="A256" s="19" t="s">
+      <c r="A256" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="B256" s="19" t="s">
+      <c r="B256" s="17" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="257" spans="1:2">
-      <c r="A257" s="5" t="s">
+      <c r="A257" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B257" s="5" t="s">
+      <c r="B257" s="3" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="258" spans="1:2">
-      <c r="A258" s="5" t="s">
+      <c r="A258" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B258" s="5" t="s">
+      <c r="B258" s="3" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="259" spans="1:2">
-      <c r="A259" s="5" t="s">
+      <c r="A259" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="B259" s="5" t="s">
+      <c r="B259" s="3" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="260" spans="1:2">
-      <c r="A260" s="5" t="s">
+      <c r="A260" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B260" s="5" t="s">
+      <c r="B260" s="3" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="263" ht="21" spans="1:1">
-      <c r="A263" s="8" t="s">
+      <c r="A263" s="7" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="265" spans="1:1">
-      <c r="A265" s="9" t="s">
+      <c r="A265" s="4" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="266" spans="1:1">
-      <c r="A266" s="9" t="s">
+      <c r="A266" s="4" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="267" spans="1:1">
-      <c r="A267" s="9" t="s">
+      <c r="A267" s="4" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="268" spans="1:1">
-      <c r="A268" s="9" t="s">
+      <c r="A268" s="4" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="269" spans="1:1">
-      <c r="A269" s="9" t="s">
+      <c r="A269" s="4" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="270" spans="1:1">
-      <c r="A270" s="9" t="s">
+      <c r="A270" s="4" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="271" spans="1:1">
-      <c r="A271" s="9" t="s">
+      <c r="A271" s="4" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="272" spans="1:1">
-      <c r="A272" s="9" t="s">
+      <c r="A272" s="4" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="273" spans="1:1">
-      <c r="A273" s="9" t="s">
+      <c r="A273" s="4" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="277" ht="21" spans="1:1">
-      <c r="A277" s="8" t="s">
+      <c r="A277" s="7" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="279" ht="17.25" spans="1:1">
-      <c r="A279" s="11" t="s">
+      <c r="A279" s="9" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="281" spans="1:1">
-      <c r="A281" s="10" t="s">
+      <c r="A281" s="8" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="283" spans="1:1">
-      <c r="A283" s="10" t="s">
+      <c r="A283" s="8" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="285" spans="1:1">
-      <c r="A285" s="10" t="s">
+      <c r="A285" s="8" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="287" spans="1:1">
-      <c r="A287" s="14" t="s">
+      <c r="A287" s="12" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="291" ht="17.25" spans="1:1">
-      <c r="A291" s="11" t="s">
+      <c r="A291" s="9" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="293" spans="1:1">
-      <c r="A293" s="10" t="s">
+      <c r="A293" s="8" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="295" spans="1:1">
-      <c r="A295" s="10" t="s">
+      <c r="A295" s="8" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="299" ht="17.25" spans="1:1">
-      <c r="A299" s="11" t="s">
+      <c r="A299" s="9" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="301" spans="1:1">
-      <c r="A301" s="10" t="s">
+      <c r="A301" s="8" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="303" spans="1:1">
-      <c r="A303" s="10" t="s">
+      <c r="A303" s="8" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="307" ht="17.25" spans="1:1">
-      <c r="A307" s="11" t="s">
+      <c r="A307" s="9" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="309" spans="1:1">
-      <c r="A309" s="10" t="s">
+      <c r="A309" s="8" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="311" spans="1:1">
-      <c r="A311" s="10" t="s">
+      <c r="A311" s="8" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="315" ht="21" spans="1:1">
-      <c r="A315" s="8" t="s">
+      <c r="A315" s="7" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="317" spans="1:2">
-      <c r="A317" s="19" t="s">
+      <c r="A317" s="17" t="s">
         <v>166</v>
       </c>
-      <c r="B317" s="19" t="s">
+      <c r="B317" s="17" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="318" spans="1:2">
-      <c r="A318" s="5" t="s">
+      <c r="A318" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B318" s="5" t="s">
+      <c r="B318" s="3" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="319" spans="1:2">
-      <c r="A319" s="5" t="s">
+      <c r="A319" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B319" s="5" t="s">
+      <c r="B319" s="3" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="320" spans="1:2">
-      <c r="A320" s="5" t="s">
+      <c r="A320" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B320" s="5" t="s">
+      <c r="B320" s="3" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="321" spans="1:2">
-      <c r="A321" s="5" t="s">
+      <c r="A321" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B321" s="5" t="s">
+      <c r="B321" s="3" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="324" ht="21" spans="1:1">
-      <c r="A324" s="8" t="s">
+      <c r="A324" s="7" t="s">
         <v>174</v>
       </c>
     </row>
@@ -6637,37 +6783,37 @@
       </c>
     </row>
     <row r="329" spans="1:1">
-      <c r="A329" s="10" t="s">
+      <c r="A329" s="8" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="331" spans="1:1">
-      <c r="A331" s="10" t="s">
+      <c r="A331" s="8" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="335" ht="21" spans="1:1">
-      <c r="A335" s="8" t="s">
+      <c r="A335" s="7" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="337" spans="1:1">
-      <c r="A337" s="10" t="s">
+      <c r="A337" s="8" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="339" spans="1:1">
-      <c r="A339" s="10" t="s">
+      <c r="A339" s="8" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="341" spans="1:1">
-      <c r="A341" s="10" t="s">
+      <c r="A341" s="8" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="343" spans="1:1">
-      <c r="A343" s="10" t="s">
+      <c r="A343" s="8" t="s">
         <v>182</v>
       </c>
     </row>
@@ -6677,22 +6823,22 @@
       </c>
     </row>
     <row r="349" spans="1:1">
-      <c r="A349" s="10" t="s">
+      <c r="A349" s="8" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="351" spans="1:1">
-      <c r="A351" s="10" t="s">
+      <c r="A351" s="8" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="353" spans="1:1">
-      <c r="A353" s="10" t="s">
+      <c r="A353" s="8" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="355" spans="1:1">
-      <c r="A355" s="10" t="s">
+      <c r="A355" s="8" t="s">
         <v>187</v>
       </c>
     </row>
@@ -6719,12 +6865,12 @@
       </c>
     </row>
     <row r="4" ht="18" spans="1:1">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="13" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:1">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="13" t="s">
         <v>190</v>
       </c>
     </row>
@@ -6734,202 +6880,202 @@
       </c>
     </row>
     <row r="11" ht="18" spans="1:1">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="13" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="8" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="8" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:1">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="13" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:1">
-      <c r="A20" s="15" t="s">
+      <c r="A20" s="13" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="12" t="s">
+      <c r="A22" s="10" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="14" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="14" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="14" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="14" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="14" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="12" t="s">
+      <c r="A30" s="10" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:1">
-      <c r="A32" s="15" t="s">
+      <c r="A32" s="13" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="12" t="s">
+      <c r="A34" s="10" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="12" t="s">
+      <c r="A35" s="10" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="12" t="s">
+      <c r="A36" s="10" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="38" ht="18" spans="1:1">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="13" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="10" t="s">
+      <c r="A40" s="8" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="42" ht="18" spans="1:1">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="13" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="8" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="48" ht="18" spans="1:1">
-      <c r="A48" s="15" t="s">
+      <c r="A48" s="13" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="12" t="s">
+      <c r="A50" s="10" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="12" t="s">
+      <c r="A51" s="10" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="55" ht="18" spans="1:1">
-      <c r="A55" s="15" t="s">
+      <c r="A55" s="13" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="12" t="s">
+      <c r="A57" s="10" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="10" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="12" t="s">
+      <c r="A59" s="10" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="12" t="s">
+      <c r="A60" s="10" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="12" t="s">
+      <c r="A61" s="10" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="65" ht="18" spans="1:1">
-      <c r="A65" s="15" t="s">
+      <c r="A65" s="13" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="14" t="s">
+      <c r="A67" s="12" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="14" t="s">
+      <c r="A68" s="12" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="14" t="s">
+      <c r="A69" s="12" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="10" t="s">
+      <c r="A72" s="8" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="10" t="s">
+      <c r="A73" s="8" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="77" ht="18" spans="1:1">
-      <c r="A77" s="15" t="s">
+      <c r="A77" s="13" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="12" t="s">
+      <c r="A79" s="10" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="12" t="s">
+      <c r="A80" s="10" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="12" t="s">
+      <c r="A81" s="10" t="s">
         <v>230</v>
       </c>
     </row>
@@ -6966,97 +7112,97 @@
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="4" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="9" t="s">
+      <c r="A8" s="4" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="4" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="4" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="4" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="4" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="4" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="4" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="4" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="4" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="4" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="4" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="4" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="4" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="4" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="30" ht="21" spans="1:1">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="32" ht="17.25" spans="1:1">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="9" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="12" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="39" ht="17.25" spans="1:1">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="9" t="s">
         <v>253</v>
       </c>
     </row>
@@ -7066,22 +7212,22 @@
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="10" t="s">
+      <c r="A43" s="8" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="10" t="s">
+      <c r="A45" s="8" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="10" t="s">
+      <c r="A47" s="8" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="51" ht="17.25" spans="1:1">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="9" t="s">
         <v>258</v>
       </c>
     </row>
@@ -7091,12 +7237,12 @@
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="9" t="s">
+      <c r="A55" s="4" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="59" ht="17.25" spans="1:1">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="9" t="s">
         <v>261</v>
       </c>
     </row>
@@ -7121,12 +7267,12 @@
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="14" t="s">
+      <c r="A69" s="12" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="73" ht="21" spans="1:1">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="7" t="s">
         <v>267</v>
       </c>
     </row>
@@ -7156,37 +7302,37 @@
       </c>
     </row>
     <row r="87" spans="1:1">
-      <c r="A87" s="10" t="s">
+      <c r="A87" s="8" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="89" spans="1:1">
-      <c r="A89" s="10" t="s">
+      <c r="A89" s="8" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="10" t="s">
+      <c r="A91" s="8" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="10"/>
+      <c r="A92" s="8"/>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="10"/>
+      <c r="A94" s="8"/>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="10"/>
+      <c r="A96" s="8"/>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="10"/>
+      <c r="A102" s="8"/>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" s="10"/>
+      <c r="A104" s="8"/>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" s="10"/>
+      <c r="A106" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7208,547 +7354,547 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="11" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="3" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="3" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="3" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="3" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="3" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="3" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="3" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="3" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="3" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="5" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>334</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="5" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="3" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="3" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="3" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="3" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="22" spans="1:6">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="3" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="23" spans="1:6">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="3" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="24" spans="1:6">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="3" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="3" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="3" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="27" spans="1:6">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="3" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="28" spans="1:6">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="3" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="29" spans="1:6">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="3" t="s">
         <v>359</v>
       </c>
     </row>
@@ -7775,214 +7921,214 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="11" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="2" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="4" ht="27" spans="1:7">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="3" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="5" ht="27" spans="1:7">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="3" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="3" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:7">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="3" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="8" ht="27" spans="1:7">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="3" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="3" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="3" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="3" t="s">
         <v>423</v>
       </c>
     </row>
@@ -8008,585 +8154,585 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:1">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="11" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="2" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="3" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="3" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="3" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="3" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="3" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="3" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="3" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="3" t="s">
         <v>469</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="3" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="5" t="s">
         <v>476</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>477</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="3" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="3" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="3" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="3" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="3" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="3" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="5" t="s">
         <v>503</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="5" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="3" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="3" t="s">
         <v>511</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="3" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="3" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="E30" s="3" t="s">
         <v>522</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="3" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="E32" s="3" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="E33" s="3" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="3" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="E35" s="3" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="3" t="s">
         <v>544</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" s="3" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="3" t="s">
         <v>552</v>
       </c>
     </row>
     <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="E39" s="3" t="s">
         <v>556</v>
       </c>
     </row>
@@ -8616,417 +8762,417 @@
       </c>
     </row>
     <row r="6" ht="28.5" spans="1:1">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>559</v>
       </c>
     </row>
     <row r="10" ht="21" spans="1:1">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>560</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="9" t="s">
+      <c r="A12" s="4" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="4" t="s">
         <v>562</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="4" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="4" t="s">
         <v>563</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="4" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="4" t="s">
         <v>565</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="4" t="s">
         <v>566</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="4" t="s">
         <v>567</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="9" t="s">
+      <c r="A21" s="4" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="9" t="s">
+      <c r="A22" s="4" t="s">
         <v>569</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="4" t="s">
         <v>570</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="9" t="s">
+      <c r="A24" s="4" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="4" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="4" t="s">
         <v>571</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="9" t="s">
+      <c r="A27" s="4" t="s">
         <v>572</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="9" t="s">
+      <c r="A28" s="4" t="s">
         <v>573</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="4" t="s">
         <v>574</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="9" t="s">
+      <c r="A30" s="4" t="s">
         <v>575</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="4" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="9" t="s">
+      <c r="A32" s="4" t="s">
         <v>576</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="9" t="s">
+      <c r="A33" s="4" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="37" ht="21" spans="1:1">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="7" t="s">
         <v>577</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="4" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="9" t="s">
+      <c r="A40" s="4" t="s">
         <v>578</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="9" t="s">
+      <c r="A41" s="4" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="4" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="9" t="s">
+      <c r="A44" s="4" t="s">
         <v>579</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="9" t="s">
+      <c r="A45" s="4" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="9" t="s">
+      <c r="A46" s="4" t="s">
         <v>580</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="9" t="s">
+      <c r="A47" s="4" t="s">
         <v>581</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="9" t="s">
+      <c r="A48" s="4" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="9" t="s">
+      <c r="A49" s="4" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="53" ht="21" spans="1:1">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="7" t="s">
         <v>582</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="9" t="s">
+      <c r="A55" s="4" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="9" t="s">
+      <c r="A56" s="4" t="s">
         <v>583</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="9" t="s">
+      <c r="A57" s="4" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="9" t="s">
+      <c r="A59" s="4" t="s">
         <v>584</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="9" t="s">
+      <c r="A60" s="4" t="s">
         <v>585</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="9" t="s">
+      <c r="A61" s="4" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="9" t="s">
+      <c r="A62" s="4" t="s">
         <v>586</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="9" t="s">
+      <c r="A63" s="4" t="s">
         <v>587</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" s="9" t="s">
+      <c r="A64" s="4" t="s">
         <v>588</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="9" t="s">
+      <c r="A65" s="4" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="66" spans="1:1">
-      <c r="A66" s="9" t="s">
+      <c r="A66" s="4" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="67" spans="1:1">
-      <c r="A67" s="9" t="s">
+      <c r="A67" s="4" t="s">
         <v>590</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="9" t="s">
+      <c r="A68" s="4" t="s">
         <v>591</v>
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" s="9" t="s">
+      <c r="A69" s="4" t="s">
         <v>592</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="9" t="s">
+      <c r="A70" s="4" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="9" t="s">
+      <c r="A71" s="4" t="s">
         <v>593</v>
       </c>
     </row>
     <row r="72" spans="1:1">
-      <c r="A72" s="9" t="s">
+      <c r="A72" s="4" t="s">
         <v>594</v>
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="9" t="s">
+      <c r="A73" s="4" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" s="9" t="s">
+      <c r="A74" s="4" t="s">
         <v>595</v>
       </c>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" s="9" t="s">
+      <c r="A75" s="4" t="s">
         <v>596</v>
       </c>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" s="9" t="s">
+      <c r="A76" s="4" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="9" t="s">
+      <c r="A77" s="4" t="s">
         <v>597</v>
       </c>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="9" t="s">
+      <c r="A78" s="4" t="s">
         <v>598</v>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="9" t="s">
+      <c r="A79" s="4" t="s">
         <v>599</v>
       </c>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="9" t="s">
+      <c r="A80" s="4" t="s">
         <v>600</v>
       </c>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" s="9" t="s">
+      <c r="A81" s="4" t="s">
         <v>601</v>
       </c>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" s="9" t="s">
+      <c r="A82" s="4" t="s">
         <v>598</v>
       </c>
     </row>
     <row r="83" spans="1:1">
-      <c r="A83" s="9" t="s">
+      <c r="A83" s="4" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="84" spans="1:1">
-      <c r="A84" s="9" t="s">
+      <c r="A84" s="4" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="85" spans="1:1">
-      <c r="A85" s="9" t="s">
+      <c r="A85" s="4" t="s">
         <v>602</v>
       </c>
     </row>
     <row r="86" spans="1:1">
-      <c r="A86" s="9" t="s">
+      <c r="A86" s="4" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="90" ht="21" spans="1:1">
-      <c r="A90" s="8" t="s">
+      <c r="A90" s="7" t="s">
         <v>603</v>
       </c>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="9" t="s">
+      <c r="A92" s="4" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="9" t="s">
+      <c r="A93" s="4" t="s">
         <v>604</v>
       </c>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="9" t="s">
+      <c r="A94" s="4" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="9" t="s">
+      <c r="A96" s="4" t="s">
         <v>605</v>
       </c>
     </row>
     <row r="97" spans="1:1">
-      <c r="A97" s="9" t="s">
+      <c r="A97" s="4" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" s="9" t="s">
+      <c r="A98" s="4" t="s">
         <v>606</v>
       </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" s="9" t="s">
+      <c r="A99" s="4" t="s">
         <v>607</v>
       </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" s="9" t="s">
+      <c r="A100" s="4" t="s">
         <v>568</v>
       </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" s="9" t="s">
+      <c r="A101" s="4" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" s="9" t="s">
+      <c r="A102" s="4" t="s">
         <v>608</v>
       </c>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" s="9" t="s">
+      <c r="A103" s="4" t="s">
         <v>561</v>
       </c>
     </row>
     <row r="107" ht="28.5" spans="1:1">
-      <c r="A107" s="7" t="s">
+      <c r="A107" s="6" t="s">
         <v>609</v>
       </c>
     </row>
     <row r="109" ht="21" spans="1:1">
-      <c r="A109" s="8" t="s">
+      <c r="A109" s="7" t="s">
         <v>610</v>
       </c>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" s="10" t="s">
+      <c r="A111" s="8" t="s">
         <v>611</v>
       </c>
     </row>
     <row r="113" spans="1:1">
-      <c r="A113" s="10" t="s">
+      <c r="A113" s="8" t="s">
         <v>612</v>
       </c>
     </row>
     <row r="115" spans="1:1">
-      <c r="A115" s="10" t="s">
+      <c r="A115" s="8" t="s">
         <v>613</v>
       </c>
     </row>
@@ -9036,7 +9182,7 @@
       </c>
     </row>
     <row r="122" ht="21" spans="1:1">
-      <c r="A122" s="8" t="s">
+      <c r="A122" s="7" t="s">
         <v>615</v>
       </c>
     </row>
@@ -9046,32 +9192,32 @@
       </c>
     </row>
     <row r="129" ht="21" spans="1:1">
-      <c r="A129" s="8" t="s">
+      <c r="A129" s="7" t="s">
         <v>617</v>
       </c>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" s="10" t="s">
+      <c r="A131" s="8" t="s">
         <v>612</v>
       </c>
     </row>
     <row r="133" spans="1:1">
-      <c r="A133" s="10" t="s">
+      <c r="A133" s="8" t="s">
         <v>613</v>
       </c>
     </row>
     <row r="137" ht="21" spans="1:1">
-      <c r="A137" s="8" t="s">
+      <c r="A137" s="7" t="s">
         <v>618</v>
       </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="9" t="s">
+      <c r="A139" s="4" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="143" ht="28.5" spans="1:1">
-      <c r="A143" s="7" t="s">
+      <c r="A143" s="6" t="s">
         <v>267</v>
       </c>
     </row>
@@ -9081,37 +9227,37 @@
       </c>
     </row>
     <row r="147" ht="17.25" spans="1:1">
-      <c r="A147" s="11" t="s">
+      <c r="A147" s="9" t="s">
         <v>620</v>
       </c>
     </row>
     <row r="149" spans="1:1">
-      <c r="A149" s="10" t="s">
+      <c r="A149" s="8" t="s">
         <v>621</v>
       </c>
     </row>
     <row r="151" spans="1:1">
-      <c r="A151" s="10" t="s">
+      <c r="A151" s="8" t="s">
         <v>622</v>
       </c>
     </row>
     <row r="153" ht="17.25" spans="1:1">
-      <c r="A153" s="11" t="s">
+      <c r="A153" s="9" t="s">
         <v>623</v>
       </c>
     </row>
     <row r="155" spans="1:1">
-      <c r="A155" s="10" t="s">
+      <c r="A155" s="8" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="157" spans="1:1">
-      <c r="A157" s="10" t="s">
+      <c r="A157" s="8" t="s">
         <v>625</v>
       </c>
     </row>
     <row r="161" ht="28.5" spans="1:1">
-      <c r="A161" s="7" t="s">
+      <c r="A161" s="6" t="s">
         <v>626</v>
       </c>
     </row>
@@ -9121,17 +9267,17 @@
       </c>
     </row>
     <row r="165" spans="1:1">
-      <c r="A165" s="10" t="s">
+      <c r="A165" s="8" t="s">
         <v>628</v>
       </c>
     </row>
     <row r="167" spans="1:1">
-      <c r="A167" s="10" t="s">
+      <c r="A167" s="8" t="s">
         <v>629</v>
       </c>
     </row>
     <row r="169" spans="1:1">
-      <c r="A169" s="10" t="s">
+      <c r="A169" s="8" t="s">
         <v>630</v>
       </c>
     </row>
@@ -9141,17 +9287,17 @@
       </c>
     </row>
     <row r="175" spans="1:1">
-      <c r="A175" s="12" t="s">
+      <c r="A175" s="10" t="s">
         <v>632</v>
       </c>
     </row>
     <row r="177" spans="1:1">
-      <c r="A177" s="12" t="s">
+      <c r="A177" s="10" t="s">
         <v>633</v>
       </c>
     </row>
     <row r="179" spans="1:1">
-      <c r="A179" s="12" t="s">
+      <c r="A179" s="10" t="s">
         <v>634</v>
       </c>
     </row>
@@ -9175,485 +9321,485 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="3" t="s">
         <v>639</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="3" t="s">
         <v>645</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="3" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>649</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>650</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>651</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>652</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>653</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>654</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>655</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>656</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>648</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>657</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>658</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>659</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>661</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>662</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>663</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="5" t="s">
         <v>664</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>665</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>666</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>667</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>668</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="5" t="s">
         <v>669</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>670</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>671</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>672</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>668</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="5" t="s">
         <v>673</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="3" t="s">
         <v>678</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="3" t="s">
         <v>678</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>682</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>683</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="5" t="s">
         <v>684</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>685</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>686</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="5" t="s">
         <v>683</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="5" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>687</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>688</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>660</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="5" t="s">
         <v>689</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="3" t="s">
         <v>693</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="3" t="s">
         <v>696</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="3" t="s">
         <v>697</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="3" t="s">
         <v>702</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>703</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="3" t="s">
         <v>705</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="3" t="s">
         <v>706</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>708</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="3" t="s">
         <v>711</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>712</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="3" t="s">
         <v>714</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="3" t="s">
         <v>715</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="3" t="s">
         <v>716</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>717</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>718</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="3" t="s">
         <v>719</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="3" t="s">
         <v>720</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="3" t="s">
         <v>721</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="3" t="s">
         <v>722</v>
       </c>
     </row>
